--- a/public/docs/Template_Cutting.xlsx
+++ b/public/docs/Template_Cutting.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\laragon\www\jai_ekanban\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DE4BA4-C1D3-4661-99DA-DA067F559D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9541C229-A7A5-4FE5-B039-A7F29D9CCEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{DB888F35-DBDA-4F92-8C17-F796FD33FFBE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Conveyor</t>
   </si>
@@ -50,21 +50,12 @@
     <t>Qty.</t>
   </si>
   <si>
-    <t>Issue</t>
-  </si>
-  <si>
     <t>Machine</t>
   </si>
   <si>
     <t>Sequence</t>
   </si>
   <si>
-    <t>Barcode Kanban</t>
-  </si>
-  <si>
-    <t>Released Date</t>
-  </si>
-  <si>
     <t>Released Note</t>
   </si>
   <si>
@@ -183,6 +174,9 @@
   </si>
   <si>
     <t>ASSY5</t>
+  </si>
+  <si>
+    <t>Carline</t>
   </si>
 </sst>
 </file>
@@ -286,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -302,6 +296,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,196 +633,188 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A02A7C30-A8FE-4581-AC4A-4E3166DD3C21}">
-  <dimension ref="A1:AW1"/>
+  <dimension ref="A1:AU1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="4.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="43" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="5.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="45" max="16384" width="9.140625" style="1"/>
+    <col min="8" max="8" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="4.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="41" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="5.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:47" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="5" t="s">
+      <c r="AS1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="4" t="s">
+      <c r="AT1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="4" t="s">
+      <c r="AU1" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="AU1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs/Template_Cutting.xlsx
+++ b/public/docs/Template_Cutting.xlsx
@@ -1,42 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\laragon\www\jai_ekanban\public\docs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9541C229-A7A5-4FE5-B039-A7F29D9CCEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{DB888F35-DBDA-4F92-8C17-F796FD33FFBE}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
+  <si>
+    <t>Carline</t>
+  </si>
   <si>
     <t>Conveyor</t>
   </si>
@@ -161,62 +143,47 @@
     <t>T06</t>
   </si>
   <si>
-    <t>ASSY1</t>
-  </si>
-  <si>
-    <t>ASSY2</t>
-  </si>
-  <si>
-    <t>ASSY3</t>
-  </si>
-  <si>
-    <t>ASSY4</t>
-  </si>
-  <si>
-    <t>ASSY5</t>
-  </si>
-  <si>
-    <t>Carline</t>
+    <t>ASSY-001</t>
+  </si>
+  <si>
+    <t>ASSY-002</t>
+  </si>
+  <si>
+    <t>ASSY-003</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="1"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -228,18 +195,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -248,31 +215,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -280,39 +233,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="3">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -327,44 +261,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -392,31 +326,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -444,23 +361,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -472,353 +372,364 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A02A7C30-A8FE-4581-AC4A-4E3166DD3C21}">
-  <dimension ref="A1:AU1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:AS1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="4.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="41" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="23" max="23" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="25" max="25" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="26" max="26" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="27" max="27" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="28" max="28" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="29" max="29" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="30" max="30" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="31" max="31" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="32" max="32" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="33" max="33" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="34" max="34" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="35" max="35" width="5.713" bestFit="true" customWidth="true" style="0"/>
+    <col min="36" max="36" width="5.713" bestFit="true" customWidth="true" style="0"/>
+    <col min="37" max="37" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="38" max="38" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="39" max="39" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="40" max="40" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="41" max="41" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="42" max="42" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="43" max="43" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="44" max="44" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="45" max="45" width="12.854" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:45">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="4" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="4" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="4" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="4" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="AU1" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
--- a/public/docs/Template_Cutting.xlsx
+++ b/public/docs/Template_Cutting.xlsx
@@ -8,14 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId4"/>
+    <sheet name="PETUNJUK" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="98">
+  <si>
+    <t>Type</t>
+  </si>
   <si>
     <t>Carline</t>
   </si>
@@ -35,9 +39,15 @@
     <t>Machine</t>
   </si>
   <si>
+    <t>Machine Twist</t>
+  </si>
+  <si>
     <t>Sequence</t>
   </si>
   <si>
+    <t>Sequence 2</t>
+  </si>
+  <si>
     <t>Released Note</t>
   </si>
   <si>
@@ -47,6 +57,18 @@
     <t>Barcode Mesin</t>
   </si>
   <si>
+    <t>Barcode Navigasi</t>
+  </si>
+  <si>
+    <t>Barcode Process</t>
+  </si>
+  <si>
+    <t>Barcode Shikake</t>
+  </si>
+  <si>
+    <t>To Store</t>
+  </si>
+  <si>
     <t>Address</t>
   </si>
   <si>
@@ -150,6 +172,144 @@
   </si>
   <si>
     <t>ASSY-003</t>
+  </si>
+  <si>
+    <t>PETUNJUK PENGISIAN TEMPLATE MASTER CIRCUIT</t>
+  </si>
+  <si>
+    <t>1. CARA MENGISI KOLOM TYPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Isi dengan "CUTTING" untuk data cutting standar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Isi dengan "CUTTING_TWIST" untuk data cutting twist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Kolom ini WAJIB diisi untuk setiap baris data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Penulisan harus HURUF KAPITAL semua</t>
+  </si>
+  <si>
+    <t>2. KETERANGAN WARNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   HIJAU - Field yang WAJIB diisi untuk SEMUA tipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - TYPE, CARLINE, CONVEYOR, CCT No., FAMILY, QTY, MACHINE, SEQUENCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - RELEASED NOTE, CUST NO., ADDRESS, CCT CODE, KIND, SIZE, COL, C/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - TERMINAL 1, TERMINAL 2, NOTE 1, NOTE 2, STRIP 1, STRIP 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - ACC. 1, ACC 2, TUBE 1, TUBE 2, MARK 1, MARK 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - TA, TB, T01-T06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   KUNING - Field KHUSUS untuk tipe CUTTING saja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - BARCODE MESIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - GOLD 1, GOLD 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - ACC. 1A, ACC 2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - REMARK 1, REMARK 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Jika TYPE = "CUTTING_TWIST", kolom ini bisa dikosongkan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   BIRU - Field KHUSUS untuk tipe CUTTING_TWIST saja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - MACHINE TWIST - Nomor mesin twist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - SEQUENCE 2 - Urutan kedua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - BARCODE NAVIGASI - Barcode untuk navigasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - BARCODE PROCESS - Barcode proses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - BARCODE SHIKAKE - Barcode shikake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - TO STORE - Tujuan penyimpanan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Jika TYPE = "CUTTING", kolom ini bisa dikosongkan</t>
+  </si>
+  <si>
+    <t>3. CONTOH PENGISIAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Contoh baris CUTTING:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   TYPE=CUTTING | CARLINE=ABC | CONVEYOR=CONV-1 | ... | BARCODE MESIN=BM001 | (kolom biru dikosongkan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Contoh baris CUTTING_TWIST:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   TYPE=CUTTING_TWIST | CARLINE=XYZ | CONVEYOR=CONV-2 | ... | MACHINE TWIST=MT001 | BARCODE NAVIGASI=NAV001</t>
+  </si>
+  <si>
+    <t>4. CATATAN PENTING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Satu file Excel bisa berisi campuran data CUTTING dan CUTTING_TWIST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Pastikan TYPE diisi dengan benar di setiap baris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Maksimal 1000 baris per upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Format file harus .xlsx atau .xls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Baris data dimulai dari baris ke-2 (baris 1 adalah header)</t>
+  </si>
+  <si>
+    <t>5. KOLOM ASSY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Kolom Assy dimulai setelah kolom T06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Isi dengan angka "1" jika circuit memiliki assy tersebut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Kosongkan jika circuit tidak memiliki assy tersebut</t>
+  </si>
+  <si>
+    <t>LEGENDA WARNA:</t>
+  </si>
+  <si>
+    <t>HIJAU</t>
+  </si>
+  <si>
+    <t>KUNING</t>
+  </si>
+  <si>
+    <t>BIRU</t>
   </si>
 </sst>
 </file>
@@ -157,7 +317,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -173,7 +333,7 @@
       <strike val="0"/>
       <u val="none"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -185,8 +345,17 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -195,7 +364,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -233,14 +414,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,57 +732,64 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AS1"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="11.569" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="18.71" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="18.71" bestFit="true" customWidth="true" style="0"/>
     <col min="12" max="12" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="23" max="23" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="25" max="25" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="26" max="26" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="27" max="27" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="20.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="20.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="23" max="23" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="25" max="25" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="26" max="26" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="27" max="27" width="11.569" bestFit="true" customWidth="true" style="0"/>
     <col min="28" max="28" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="29" max="29" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="30" max="30" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="30" max="30" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="31" max="31" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="32" max="32" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="33" max="33" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="34" max="34" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="35" max="35" width="5.713" bestFit="true" customWidth="true" style="0"/>
-    <col min="36" max="36" width="5.713" bestFit="true" customWidth="true" style="0"/>
-    <col min="37" max="37" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="38" max="38" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="39" max="39" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="40" max="40" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="41" max="41" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="42" max="42" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="43" max="43" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="44" max="44" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="45" max="45" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="32" max="32" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="33" max="33" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="34" max="34" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="35" max="35" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="36" max="36" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="37" max="37" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="38" max="38" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="39" max="39" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="40" max="40" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="41" max="41" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="42" max="42" width="5.713" bestFit="true" customWidth="true" style="0"/>
+    <col min="43" max="43" width="5.713" bestFit="true" customWidth="true" style="0"/>
+    <col min="44" max="44" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="45" max="45" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="46" max="46" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="47" max="47" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="48" max="48" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="49" max="49" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="50" max="50" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="51" max="51" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="52" max="52" width="12.854" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45">
+    <row r="1" spans="1:52">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -612,13 +811,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -627,19 +826,19 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -666,7 +865,7 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
@@ -675,7 +874,7 @@
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
@@ -684,7 +883,7 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="1" t="s">
@@ -693,7 +892,7 @@
       <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="1" t="s">
@@ -702,7 +901,7 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
       <c r="AM1" s="1" t="s">
@@ -711,20 +910,299 @@
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="3" t="s">
         <v>40</v>
       </c>
       <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:B57"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="100" customWidth="true" style="0"/>
+    <col min="2" max="2" width="30" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" t="str">
+        <f> Wajib untuk SEMUA tipe</f>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" t="str">
+        <f> Khusus CUTTING saja</f>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" t="str">
+        <f> Khusus CUTTING_TWIST saja</f>
       </c>
     </row>
   </sheetData>

--- a/public/docs/Template_Cutting.xlsx
+++ b/public/docs/Template_Cutting.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="91">
   <si>
     <t>Type</t>
   </si>
@@ -99,21 +99,18 @@
     <t>Strip 1</t>
   </si>
   <si>
-    <t>Acc. 1</t>
-  </si>
-  <si>
     <t>Acc. 1A</t>
   </si>
   <si>
+    <t>Acc. 1B</t>
+  </si>
+  <si>
     <t>Tube 1</t>
   </si>
   <si>
     <t>Mark 1</t>
   </si>
   <si>
-    <t>Remark 1</t>
-  </si>
-  <si>
     <t>Terminal 2</t>
   </si>
   <si>
@@ -126,27 +123,18 @@
     <t>Strip 2</t>
   </si>
   <si>
-    <t>Acc 2</t>
-  </si>
-  <si>
     <t>Acc 2A</t>
   </si>
   <si>
+    <t>Acc 2B</t>
+  </si>
+  <si>
     <t>Tube 2</t>
   </si>
   <si>
     <t>Mark 2</t>
   </si>
   <si>
-    <t>Remark 2</t>
-  </si>
-  <si>
-    <t>TA</t>
-  </si>
-  <si>
-    <t>TB</t>
-  </si>
-  <si>
     <t>T01</t>
   </si>
   <si>
@@ -156,13 +144,7 @@
     <t>T03</t>
   </si>
   <si>
-    <t>T04</t>
-  </si>
-  <si>
-    <t>T05</t>
-  </si>
-  <si>
-    <t>T06</t>
+    <t>Memory Twist</t>
   </si>
   <si>
     <t>ASSY-001</t>
@@ -207,10 +189,10 @@
     <t xml:space="preserve">   - TERMINAL 1, TERMINAL 2, NOTE 1, NOTE 2, STRIP 1, STRIP 2</t>
   </si>
   <si>
-    <t xml:space="preserve">   - ACC. 1, ACC 2, TUBE 1, TUBE 2, MARK 1, MARK 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - TA, TB, T01-T06</t>
+    <t xml:space="preserve">   - ACC. 1B, ACC 2B, TUBE 1, TUBE 2, MARK 1, MARK 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - TO STORE, T01-T03</t>
   </si>
   <si>
     <t xml:space="preserve">   KUNING - Field KHUSUS untuk tipe CUTTING saja</t>
@@ -225,9 +207,6 @@
     <t xml:space="preserve">   - ACC. 1A, ACC 2A</t>
   </si>
   <si>
-    <t xml:space="preserve">   - REMARK 1, REMARK 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">   - Jika TYPE = "CUTTING_TWIST", kolom ini bisa dikosongkan</t>
   </si>
   <si>
@@ -249,7 +228,7 @@
     <t xml:space="preserve">   - BARCODE SHIKAKE - Barcode shikake</t>
   </si>
   <si>
-    <t xml:space="preserve">   - TO STORE - Tujuan penyimpanan</t>
+    <t xml:space="preserve">   - MEMORY TWIST - Memory twist value</t>
   </si>
   <si>
     <t xml:space="preserve">   - Jika TYPE = "CUTTING", kolom ini bisa dikosongkan</t>
@@ -291,7 +270,7 @@
     <t>5. KOLOM ASSY</t>
   </si>
   <si>
-    <t xml:space="preserve">   - Kolom Assy dimulai setelah kolom T06</t>
+    <t xml:space="preserve">   - Kolom Assy dimulai setelah kolom T03</t>
   </si>
   <si>
     <t xml:space="preserve">   - Isi dengan angka "1" jika circuit memiliki assy tersebut</t>
@@ -732,7 +711,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AZ1"/>
+  <dimension ref="A1:AT1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
@@ -762,34 +741,28 @@
     <col min="25" max="25" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="26" max="26" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="27" max="27" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="28" max="28" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="28" max="28" width="11.569" bestFit="true" customWidth="true" style="0"/>
     <col min="29" max="29" width="11.569" bestFit="true" customWidth="true" style="0"/>
     <col min="30" max="30" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="31" max="31" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="32" max="32" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="33" max="33" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="32" max="32" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="33" max="33" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="34" max="34" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="35" max="35" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="36" max="36" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="37" max="37" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="35" max="35" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="36" max="36" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="37" max="37" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="38" max="38" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="39" max="39" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="40" max="40" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="41" max="41" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="42" max="42" width="5.713" bestFit="true" customWidth="true" style="0"/>
-    <col min="43" max="43" width="5.713" bestFit="true" customWidth="true" style="0"/>
-    <col min="44" max="44" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="45" max="45" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="46" max="46" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="47" max="47" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="48" max="48" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="49" max="49" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="50" max="50" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="51" max="51" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="52" max="52" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="40" max="40" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="41" max="41" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="42" max="42" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="43" max="43" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="44" max="44" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="45" max="45" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="46" max="46" width="12.854" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52">
+    <row r="1" spans="1:46">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -838,7 +811,7 @@
       <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -871,10 +844,10 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
@@ -883,25 +856,25 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="AM1" s="1" t="s">
@@ -910,41 +883,23 @@
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -959,7 +914,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="true" style="0"/>
@@ -968,240 +923,235 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>70</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>79</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="6" t="s">
-        <v>94</v>
+      <c r="A54" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B54" t="str">
+        <f> Wajib untuk SEMUA tipe</f>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="7" t="s">
-        <v>95</v>
+      <c r="A55" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="B55" t="str">
-        <f> Wajib untuk SEMUA tipe</f>
+        <f> Khusus CUTTING saja</f>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="8" t="s">
-        <v>96</v>
+      <c r="A56" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="B56" t="str">
-        <f> Khusus CUTTING saja</f>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B57" t="str">
         <f> Khusus CUTTING_TWIST saja</f>
       </c>
     </row>

--- a/public/docs/Template_Cutting.xlsx
+++ b/public/docs/Template_Cutting.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
   <si>
     <t>Type</t>
   </si>
@@ -74,6 +74,9 @@
     <t>CCT Code</t>
   </si>
   <si>
+    <t>Shikake Code</t>
+  </si>
+  <si>
     <t>Kind</t>
   </si>
   <si>
@@ -164,7 +167,7 @@
     <t>T06</t>
   </si>
   <si>
-    <t>MEMORI TWIST</t>
+    <t>Memory Twist</t>
   </si>
   <si>
     <t>ASSY-001</t>
@@ -564,7 +567,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:BA1"/>
+  <dimension ref="A1:BB1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
@@ -586,43 +589,44 @@
     <col min="17" max="17" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="18" max="18" width="11.569" bestFit="true" customWidth="true" style="0"/>
     <col min="19" max="19" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="17.567" bestFit="true" customWidth="true" style="0"/>
     <col min="21" max="21" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="23" max="23" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="25" max="25" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="25" max="25" width="15.139" bestFit="true" customWidth="true" style="0"/>
     <col min="26" max="26" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="27" max="27" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="28" max="28" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="29" max="29" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="30" max="30" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="27" max="27" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="28" max="28" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="29" max="29" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="30" max="30" width="11.569" bestFit="true" customWidth="true" style="0"/>
     <col min="31" max="31" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="32" max="32" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="33" max="33" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="34" max="34" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="32" max="32" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="33" max="33" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="34" max="34" width="15.139" bestFit="true" customWidth="true" style="0"/>
     <col min="35" max="35" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="36" max="36" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="37" max="37" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="38" max="38" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="36" max="36" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="37" max="37" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="38" max="38" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="39" max="39" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="40" max="40" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="41" max="41" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="42" max="42" width="5.713" bestFit="true" customWidth="true" style="0"/>
+    <col min="41" max="41" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="42" max="42" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="43" max="43" width="5.713" bestFit="true" customWidth="true" style="0"/>
-    <col min="44" max="44" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="44" max="44" width="5.713" bestFit="true" customWidth="true" style="0"/>
     <col min="45" max="45" width="6.856" bestFit="true" customWidth="true" style="0"/>
     <col min="46" max="46" width="6.856" bestFit="true" customWidth="true" style="0"/>
     <col min="47" max="47" width="6.856" bestFit="true" customWidth="true" style="0"/>
     <col min="48" max="48" width="6.856" bestFit="true" customWidth="true" style="0"/>
     <col min="49" max="49" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="50" max="50" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="51" max="51" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="50" max="50" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="51" max="51" width="17.567" bestFit="true" customWidth="true" style="0"/>
     <col min="52" max="52" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="53" max="53" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="54" max="54" width="12.854" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53">
+    <row r="1" spans="1:54">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -773,7 +777,7 @@
       <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AZ1" s="2" t="s">
@@ -781,6 +785,9 @@
       </c>
       <c r="BA1" s="2" t="s">
         <v>52</v>
+      </c>
+      <c r="BB1" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs/Template_Cutting.xlsx
+++ b/public/docs/Template_Cutting.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
   <si>
     <t>Type</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>Barcode Shikake</t>
+  </si>
+  <si>
+    <t>Barcode Twist</t>
+  </si>
+  <si>
+    <t>QRCode Drawing</t>
   </si>
   <si>
     <t>To Store</t>
@@ -567,7 +573,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:BB1"/>
+  <dimension ref="A1:BD1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
@@ -586,47 +592,49 @@
     <col min="14" max="14" width="22.28" bestFit="true" customWidth="true" style="0"/>
     <col min="15" max="15" width="20.995" bestFit="true" customWidth="true" style="0"/>
     <col min="16" max="16" width="20.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="19.852" bestFit="true" customWidth="true" style="0"/>
     <col min="19" max="19" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="23" max="23" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="25" max="25" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="26" max="26" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="27" max="27" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="28" max="28" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="23" max="23" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="25" max="25" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="26" max="26" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="27" max="27" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="28" max="28" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="29" max="29" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="30" max="30" width="11.569" bestFit="true" customWidth="true" style="0"/>
     <col min="31" max="31" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="32" max="32" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="33" max="33" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="34" max="34" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="35" max="35" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="36" max="36" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="37" max="37" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="38" max="38" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="39" max="39" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="40" max="40" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="32" max="32" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="33" max="33" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="34" max="34" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="35" max="35" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="36" max="36" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="37" max="37" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="38" max="38" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="39" max="39" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="40" max="40" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="41" max="41" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="42" max="42" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="43" max="43" width="5.713" bestFit="true" customWidth="true" style="0"/>
-    <col min="44" max="44" width="5.713" bestFit="true" customWidth="true" style="0"/>
-    <col min="45" max="45" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="46" max="46" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="42" max="42" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="43" max="43" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="44" max="44" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="45" max="45" width="5.713" bestFit="true" customWidth="true" style="0"/>
+    <col min="46" max="46" width="5.713" bestFit="true" customWidth="true" style="0"/>
     <col min="47" max="47" width="6.856" bestFit="true" customWidth="true" style="0"/>
     <col min="48" max="48" width="6.856" bestFit="true" customWidth="true" style="0"/>
     <col min="49" max="49" width="6.856" bestFit="true" customWidth="true" style="0"/>
     <col min="50" max="50" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="51" max="51" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="52" max="52" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="53" max="53" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="51" max="51" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="52" max="52" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="53" max="53" width="17.567" bestFit="true" customWidth="true" style="0"/>
     <col min="54" max="54" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="55" max="55" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="56" max="56" width="12.854" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54">
+    <row r="1" spans="1:56">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -780,14 +788,20 @@
       <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="BB1" s="2" t="s">
         <v>53</v>
+      </c>
+      <c r="BC1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
